--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,18 +1712,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1738,26 +1738,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1768,26 +1768,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1798,22 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,19 +1858,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1888,18 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,18 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,15 +2402,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2420,22 +2428,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,19 +2450,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,18 +2516,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2886,26 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,22 +3558,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,12 +3584,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3603,11 +3599,11 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3618,26 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3648,26 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3678,18 +3670,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,18 +3700,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,26 +3730,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4096,22 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,18 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,26 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,16 +4604,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4634,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4664,22 +4660,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4694,26 +4690,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4724,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4754,16 +4746,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,16 +4772,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4798,12 +4802,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4820,24 +4824,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4850,20 +4846,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4876,26 +4868,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4906,22 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,22 +4928,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4962,26 +4958,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,20 +4988,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5018,18 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5378,18 +5378,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5404,22 +5404,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,26 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5460,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5494,22 +5490,26 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,22 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,22 +6268,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -6294,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,22 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,18 +6382,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6560,22 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6586,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6616,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6646,22 +6650,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,18 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,22 +7372,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7394,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7424,22 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,18 +7642,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -7664,18 +7664,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -7816,17 +7816,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -7842,12 +7842,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7864,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,19 +7908,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,22 +7930,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7960,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7982,18 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8004,15 +8000,19 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>3</v>
@@ -8096,18 +8096,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,22 +8122,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,22 +8148,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8182,26 +8178,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8212,18 +8208,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8238,26 +8234,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8268,22 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8294,18 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8320,26 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -8542,20 +8542,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="n">
         <v>2</v>
       </c>
@@ -8568,22 +8560,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8586,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8616,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8646,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,26 +8676,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -8718,22 +8706,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8748,22 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8778,12 +8766,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -8804,12 +8792,24 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -8930,22 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8956,22 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8982,26 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9012,22 +9016,18 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9042,26 +9042,26 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9616,18 +9616,22 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9642,14 +9646,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -9660,22 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9686,22 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,17 +9928,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -9954,15 +9954,19 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>3</v>
@@ -9976,12 +9980,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,12 +10002,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10068,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10090,22 +10094,18 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10378,14 +10378,14 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,14 +10450,14 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,14 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,22 +10928,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10950,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -10972,22 +10976,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -10998,22 +11002,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11028,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11072,18 +11076,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,22 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -11504,18 +11500,14 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11556,14 +11548,18 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11578,18 +11574,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -12210,14 +12210,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12228,7 +12232,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12246,18 +12250,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
@@ -12474,22 +12474,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12522,18 +12518,18 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F507" t="n">
@@ -12548,14 +12544,14 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F508" t="n">
@@ -12570,18 +12566,22 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -13086,12 +13086,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F535" t="n">
         <v>3</v>
       </c>
@@ -13104,18 +13108,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F536" t="n">
@@ -13130,7 +13134,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13148,16 +13152,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13170,18 +13170,22 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F539" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -13192,7 +13196,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13210,22 +13214,18 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13504,7 +13504,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -13540,7 +13540,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -14380,18 +14380,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14402,18 +14406,18 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -14428,22 +14432,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -14454,22 +14454,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -14480,18 +14480,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -14900,14 +14900,18 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr"/>
-      <c r="E626" t="inlineStr"/>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F626" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="627">
@@ -14954,18 +14958,14 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr"/>
-      <c r="E629" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E629" t="inlineStr"/>
       <c r="F629" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="630">
@@ -15088,14 +15088,14 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr"/>
       <c r="F636" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="637">
@@ -15106,14 +15106,14 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr"/>
       <c r="F637" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="638">
@@ -15394,14 +15394,14 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr"/>
       <c r="F653" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="654">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15430,14 +15430,14 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr"/>
       <c r="F655" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="656">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15898,14 +15898,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -15934,14 +15934,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -15988,14 +15988,14 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
@@ -16006,14 +16006,14 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,18 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1738,19 +1742,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1768,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,26 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1858,18 +1858,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,18 +2332,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2354,12 +2358,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,22 +2380,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2402,19 +2402,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2428,12 +2424,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2450,15 +2446,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,18 +2472,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2516,22 +2520,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2886,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2968,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3088,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,10 +3330,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,18 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3584,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3614,26 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3644,18 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3670,12 +3674,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3685,11 +3689,11 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3700,26 +3704,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3730,22 +3734,18 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,22 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,26 +4096,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4156,18 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4186,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,20 +4612,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4630,26 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4660,22 +4664,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4690,22 +4694,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4716,26 +4724,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4746,20 +4754,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4772,24 +4776,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4802,16 +4798,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4824,12 +4828,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4846,16 +4850,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,26 +4876,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4898,26 +4906,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4928,22 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4958,26 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4988,16 +4992,20 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5010,26 +5018,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5378,22 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5404,22 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,18 +5438,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5460,22 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5490,26 +5494,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,22 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6360,18 +6360,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6382,22 +6386,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6560,26 +6560,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6586,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,22 +6616,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6646,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,22 +7342,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7372,26 +7368,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -7402,22 +7394,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7424,22 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,18 +7664,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -7816,22 +7816,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -7842,15 +7838,19 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>3</v>
@@ -7864,18 +7864,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7886,12 +7890,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,12 +7934,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7952,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7974,17 +7978,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -8000,19 +8004,15 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>3</v>
@@ -8096,18 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,22 +8126,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8148,26 +8156,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8178,26 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -8208,18 +8212,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8234,26 +8238,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,22 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8324,18 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8542,12 +8542,24 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F327" t="n">
         <v>2</v>
       </c>
@@ -8560,12 +8572,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -8586,22 +8598,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8616,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8646,22 +8658,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8676,26 +8688,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8706,26 +8718,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8736,22 +8748,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,20 +8774,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="n">
         <v>2</v>
       </c>
@@ -8792,26 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -8930,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8960,18 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8990,22 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9042,26 +9046,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9616,22 +9616,18 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9646,22 +9642,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -9672,14 +9660,22 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9686,22 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,22 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9980,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10002,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10024,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10046,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,17 +10064,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -10094,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,15 +10112,19 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>3</v>
@@ -10378,14 +10378,14 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,14 +10432,14 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,18 +10902,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,18 +10924,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -10950,22 +10950,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10976,22 +10972,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -11002,22 +10998,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -11028,18 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -11050,22 +11050,18 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11076,14 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,18 +11478,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11500,14 +11504,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11548,18 +11556,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11574,22 +11578,18 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -12210,18 +12210,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -12232,14 +12228,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
@@ -12474,18 +12474,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -12566,22 +12570,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -13086,18 +13086,22 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -13108,22 +13112,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13152,12 +13152,16 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13170,18 +13174,18 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F539" t="n">
@@ -13196,7 +13200,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13214,16 +13218,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
         <v>3</v>
       </c>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -14380,18 +14380,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F600" t="n">
@@ -14406,22 +14406,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -14432,18 +14432,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -14454,18 +14458,18 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
@@ -14480,22 +14484,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15898,14 +15898,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -15934,14 +15934,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16006,14 +16006,14 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="688">
@@ -16060,14 +16060,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="691">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,18 +1742,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1768,26 +1768,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1798,22 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,19 +1828,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1858,18 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,26 +1884,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,22 +2332,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2380,18 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2402,15 +2402,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2424,18 +2428,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,19 +2454,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,22 +2476,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,18 +3614,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3644,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3674,26 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3704,26 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3734,18 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,26 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4066,22 +4062,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,22 +4092,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,26 +4122,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4156,22 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,18 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,16 +4604,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4634,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4664,22 +4660,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4694,26 +4690,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4724,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4754,16 +4746,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,12 +4772,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4798,24 +4794,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4828,16 +4816,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4850,20 +4846,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4876,26 +4868,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4906,22 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,22 +4928,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4962,26 +4958,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,20 +4988,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5018,18 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5378,26 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,22 +5404,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,22 +5434,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5494,18 +5494,18 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,22 +6202,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6228,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6250,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,22 +6364,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6560,22 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6586,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6616,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6646,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,22 +6736,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,18 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,22 +7372,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7394,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7424,22 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,18 +7620,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,19 +7838,15 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>3</v>
@@ -7864,17 +7860,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -7890,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7912,12 +7908,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7934,18 +7930,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,15 +7956,19 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>3</v>
@@ -7978,22 +7982,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,22 +8096,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8126,22 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,18 +8152,18 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8182,26 +8178,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8212,18 +8208,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8238,26 +8238,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8268,26 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8298,22 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -8324,18 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8572,20 +8572,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8598,22 +8590,18 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,26 +8616,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8646,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8688,26 +8676,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -8718,22 +8706,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8748,12 +8736,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -8774,12 +8762,24 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F335" t="n">
         <v>2</v>
       </c>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -8930,26 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8986,18 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,26 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9046,22 +9042,26 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9616,18 +9616,22 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9642,14 +9646,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -9660,22 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9686,22 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,17 +9950,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,15 +10020,19 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>3</v>
@@ -10042,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10068,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10112,22 +10112,22 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,14 +10396,14 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,14 +10432,14 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="407">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,14 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,22 +10928,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10950,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -10972,22 +10976,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -10998,22 +11002,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11028,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11072,18 +11076,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,22 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -11504,18 +11500,14 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11556,14 +11548,18 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11578,18 +11574,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12228,18 +12228,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12250,14 +12246,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -12474,22 +12474,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12570,18 +12566,22 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -13086,18 +13086,18 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F535" t="n">
@@ -13112,16 +13112,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13134,7 +13130,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13152,18 +13148,22 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -13174,22 +13174,18 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="540">
@@ -13200,7 +13196,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13218,12 +13214,16 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr"/>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F541" t="n">
         <v>3</v>
       </c>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -14380,22 +14380,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14406,22 +14402,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14432,18 +14428,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -14458,22 +14454,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
@@ -14484,18 +14480,22 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F604" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="605">
@@ -14506,18 +14506,18 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F605" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15898,14 +15898,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -15934,14 +15934,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15970,14 +15970,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16060,14 +16060,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="691">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,26 +1712,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1742,18 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1768,19 +1772,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1798,26 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,18 +1828,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,22 +2376,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2402,19 +2398,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2428,22 +2420,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2454,15 +2442,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2476,18 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,18 +2516,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2942,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2968,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3088,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,10 +3330,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3588,18 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,26 +3618,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3644,26 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,22 +3674,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,18 +3700,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3745,11 +3745,11 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,18 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4062,26 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4092,22 +4092,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,22 +4122,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,26 +4152,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,20 +4612,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4630,26 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4660,22 +4664,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4690,22 +4694,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4716,26 +4724,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4746,20 +4754,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4772,16 +4776,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4794,12 +4806,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4816,24 +4828,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4846,16 +4850,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,26 +4876,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4898,26 +4906,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4928,22 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4958,26 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4988,16 +4992,20 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5010,26 +5018,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5378,18 +5378,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5404,22 +5404,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,26 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5460,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5494,22 +5490,26 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,22 +6176,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6202,22 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6228,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6250,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6272,18 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,22 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6560,26 +6560,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6586,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6616,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6650,22 +6646,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,22 +7342,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7372,26 +7368,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -7402,22 +7394,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7424,22 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,18 +7620,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,18 +7686,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -7816,18 +7816,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -7838,12 +7842,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,22 +7864,18 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -7886,15 +7886,19 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7908,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,17 +7934,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
@@ -7956,19 +7960,15 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>3</v>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,22 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8122,26 +8126,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -8152,18 +8152,18 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8178,26 +8178,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -8208,22 +8208,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8238,26 +8234,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8268,18 +8264,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,22 +8290,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8324,18 +8320,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,12 +8572,24 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8590,12 +8602,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -8616,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8646,22 +8658,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8676,26 +8688,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8706,22 +8718,18 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8736,20 +8744,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8762,26 +8762,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8792,26 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -8930,22 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8956,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8990,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9012,26 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9046,18 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9616,22 +9616,18 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9646,22 +9642,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -9672,14 +9660,22 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9686,22 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,22 +9950,18 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -9976,12 +9972,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,15 +9994,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10020,22 +10020,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10112,17 +10112,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,14 +10396,14 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
@@ -10414,14 +10414,14 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,18 +10902,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,18 +10924,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -10950,22 +10950,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10976,22 +10972,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -11002,22 +10998,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -11028,18 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -11050,22 +11050,18 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11076,14 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,18 +11478,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11500,14 +11504,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11548,18 +11556,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11574,22 +11578,18 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -12210,14 +12210,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12228,7 +12232,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12246,18 +12250,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12474,18 +12474,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -12566,22 +12570,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -13086,22 +13086,18 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13112,12 +13108,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13148,18 +13148,18 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F538" t="n">
@@ -13174,16 +13174,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13196,7 +13192,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13214,18 +13210,22 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -14380,18 +14380,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14402,18 +14406,18 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -14428,22 +14432,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -14454,22 +14454,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -14480,18 +14480,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15898,14 +15898,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -15934,14 +15934,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -15952,14 +15952,14 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr"/>
       <c r="F684" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
@@ -15970,14 +15970,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16060,7 +16060,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,19 +1712,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1742,22 +1738,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,18 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1888,18 +1888,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,18 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,15 +2402,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2420,22 +2428,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,19 +2450,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,18 +2516,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,26 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3648,26 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3678,26 +3670,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3708,18 +3700,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3734,18 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4096,22 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,18 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,26 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,16 +4604,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4634,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4664,22 +4660,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4694,26 +4690,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4724,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4754,16 +4746,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,16 +4772,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4798,12 +4802,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4820,24 +4824,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4850,20 +4846,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4876,26 +4868,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4906,22 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,22 +4928,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4962,26 +4958,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,20 +4988,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5018,18 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5378,18 +5378,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5404,22 +5404,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,26 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5460,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5494,22 +5490,26 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,22 +6202,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6228,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6250,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,22 +6364,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6560,22 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6586,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6616,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6646,22 +6650,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,18 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,22 +7372,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7394,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7424,22 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,18 +7664,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,15 +7838,19 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>3</v>
@@ -7860,17 +7864,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -7886,12 +7890,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,18 +7934,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7952,12 +7960,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7974,22 +7982,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8000,19 +8004,15 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>3</v>
@@ -8096,18 +8096,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,18 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8148,22 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8174,26 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8204,26 +8212,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8234,26 +8238,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8264,22 +8268,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,18 +8294,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8542,22 +8542,18 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,26 +8568,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8602,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8632,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8662,20 +8658,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
         <v>2</v>
       </c>
@@ -8688,26 +8676,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -8718,12 +8706,24 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F333" t="n">
         <v>2</v>
       </c>
@@ -8736,22 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,22 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -8930,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8960,18 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8990,22 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9042,26 +9046,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9616,18 +9616,22 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9642,14 +9646,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -9660,22 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9686,22 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,22 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,22 +9998,18 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -10024,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10046,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,15 +10064,19 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>3</v>
@@ -10090,17 +10090,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -10116,12 +10116,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10378,14 +10378,14 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,14 +10432,14 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,14 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,22 +10928,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10950,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -10972,22 +10976,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -10998,22 +11002,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11028,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11072,18 +11076,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,22 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -11504,18 +11500,14 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11556,14 +11548,18 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11578,18 +11574,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -12210,14 +12210,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12228,7 +12232,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12246,18 +12250,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12474,22 +12474,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12570,18 +12566,22 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -13086,18 +13086,22 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -13108,22 +13112,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13152,12 +13152,16 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13170,18 +13174,18 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F539" t="n">
@@ -13196,7 +13200,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13214,16 +13218,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
         <v>3</v>
       </c>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -14380,18 +14380,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14402,18 +14406,18 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -14428,22 +14432,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -14454,22 +14454,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -14480,18 +14480,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15898,14 +15898,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -15934,14 +15934,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -15988,14 +15988,14 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
@@ -16006,14 +16006,14 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,18 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1738,19 +1742,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1768,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,26 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1858,18 +1858,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,22 +2332,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2380,18 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2402,15 +2402,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2424,18 +2428,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,19 +2454,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,22 +2476,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,26 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,22 +3558,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,12 +3584,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3603,11 +3599,11 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3618,18 +3614,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3644,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3674,18 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3700,26 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3730,26 +3730,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,26 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4066,22 +4062,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,22 +4092,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,26 +4122,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4156,22 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,18 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,16 +4604,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4634,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4664,22 +4660,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4694,26 +4690,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4724,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4754,16 +4746,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,12 +4772,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4798,24 +4794,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4828,16 +4816,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4850,20 +4846,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4876,26 +4868,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4906,22 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,22 +4928,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4962,26 +4958,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,20 +4988,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5018,18 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5378,26 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,22 +5404,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,22 +5434,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5494,18 +5494,18 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,22 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,22 +6268,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -6294,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,22 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,18 +6382,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6560,22 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6586,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6616,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6646,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,22 +6736,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,18 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,22 +7372,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7394,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7424,22 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,18 +7620,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,18 +7686,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -7816,17 +7816,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -7842,12 +7842,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7864,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,15 +7886,19 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7908,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,22 +7934,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7956,19 +7956,15 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>3</v>
@@ -7982,18 +7978,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,18 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,22 +8126,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8148,26 +8156,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8178,26 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8208,18 +8212,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8234,26 +8238,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8264,22 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8324,18 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8542,20 +8542,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="n">
         <v>2</v>
       </c>
@@ -8568,22 +8560,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8586,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,26 +8616,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8646,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,26 +8676,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -8718,22 +8706,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8748,22 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8778,12 +8766,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -8804,12 +8792,24 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -8930,22 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8956,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8990,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9012,26 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9046,18 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9616,18 +9616,22 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9642,14 +9646,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -9660,22 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9686,22 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,22 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9980,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10002,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10024,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10046,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,17 +10064,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -10094,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,15 +10112,19 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>3</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,14 +10396,14 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
@@ -10414,14 +10414,14 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,14 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,22 +10928,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10950,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -10972,22 +10976,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -10998,22 +11002,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11028,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11072,18 +11076,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,22 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -11504,18 +11500,14 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11556,14 +11548,18 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11578,18 +11574,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12228,18 +12228,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12250,14 +12246,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -12474,22 +12474,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12570,18 +12566,22 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -13086,22 +13086,18 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13112,12 +13108,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13148,18 +13148,18 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F538" t="n">
@@ -13174,16 +13174,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13196,7 +13192,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13214,18 +13210,22 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -14380,22 +14380,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14406,22 +14402,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14432,18 +14428,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -14458,22 +14454,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
@@ -14484,18 +14480,22 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F604" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="605">
@@ -14506,18 +14506,18 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F605" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15898,14 +15898,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -15934,14 +15934,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15970,14 +15970,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16060,14 +16060,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="691">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,19 +1712,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1742,22 +1738,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,18 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1888,18 +1888,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,18 +2332,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2354,12 +2358,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,22 +2380,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2402,19 +2402,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2428,12 +2424,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2450,15 +2446,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,18 +2472,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2516,22 +2520,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2886,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2968,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3088,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,10 +3330,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,18 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3584,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3614,26 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3644,18 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3670,12 +3674,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3685,11 +3689,11 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3700,26 +3704,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3730,22 +3734,18 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,22 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,26 +4096,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4156,18 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4186,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,20 +4612,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4630,26 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4660,22 +4664,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4690,22 +4694,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4716,26 +4724,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4746,20 +4754,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4772,24 +4776,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4802,16 +4798,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4824,12 +4828,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4846,16 +4850,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,26 +4876,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4898,26 +4906,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4928,22 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4958,26 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4988,16 +4992,20 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5010,26 +5018,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5378,22 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5404,22 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,18 +5438,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5460,22 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5490,26 +5494,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,22 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6360,18 +6360,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6382,22 +6386,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6560,26 +6560,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6586,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,22 +6616,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6646,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,22 +7342,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7372,26 +7368,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -7402,22 +7394,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7424,22 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,18 +7620,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,18 +7686,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -7816,22 +7816,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -7842,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7864,18 +7860,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7886,15 +7886,19 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7908,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,12 +7934,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7952,19 +7956,15 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>3</v>
@@ -7978,17 +7978,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,18 +8096,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,18 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8148,22 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8174,26 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -8204,26 +8212,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8234,26 +8238,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,22 +8268,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,18 +8294,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,22 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8602,12 +8602,24 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F329" t="n">
         <v>2</v>
       </c>
@@ -8620,26 +8632,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8650,12 +8662,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -8676,26 +8688,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8706,20 +8718,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="n">
         <v>2</v>
       </c>
@@ -8732,26 +8736,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8762,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8792,22 +8796,18 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -8930,22 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8956,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8990,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9012,26 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9046,18 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9616,22 +9616,18 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9646,22 +9642,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -9672,14 +9660,22 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9686,22 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,22 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,22 +9998,18 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -10024,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10046,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,15 +10064,19 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>3</v>
@@ -10090,17 +10090,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -10116,12 +10116,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,14 +10396,14 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
@@ -10414,14 +10414,14 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,18 +10902,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,18 +10924,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -10950,22 +10950,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10976,22 +10972,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -11002,22 +10998,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -11028,18 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -11050,22 +11050,18 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11076,14 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,18 +11478,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11500,14 +11504,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11548,18 +11556,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11574,22 +11578,18 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -12210,18 +12210,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -12232,14 +12228,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
@@ -12474,18 +12474,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -12566,22 +12570,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -13086,22 +13086,18 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13112,12 +13108,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13148,18 +13148,18 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F538" t="n">
@@ -13174,16 +13174,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13196,7 +13192,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13214,18 +13210,22 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -14380,18 +14380,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F600" t="n">
@@ -14406,22 +14406,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -14432,18 +14432,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -14454,18 +14458,18 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
@@ -14480,22 +14484,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15898,14 +15898,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -15934,14 +15934,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16006,14 +16006,14 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="688">
@@ -16060,14 +16060,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="691">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,18 +1712,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1738,26 +1738,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1768,26 +1768,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1798,22 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,19 +1858,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1888,18 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,22 +2332,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2380,18 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2402,15 +2402,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2424,18 +2428,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,19 +2454,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,22 +2476,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,18 +3614,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3644,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3674,26 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3704,26 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3734,18 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,26 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4066,22 +4062,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,22 +4092,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,26 +4122,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4156,22 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,18 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,16 +4604,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4634,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4664,22 +4660,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4694,26 +4690,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4724,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4754,16 +4746,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,12 +4772,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -4798,24 +4794,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4828,16 +4816,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4850,20 +4846,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4876,26 +4868,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4906,22 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,22 +4928,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4962,26 +4958,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,20 +4988,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5018,18 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5378,26 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,22 +5404,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,22 +5434,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5494,18 +5494,18 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,22 +6202,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6228,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6250,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,22 +6364,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6560,22 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6586,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6616,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6646,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,22 +6736,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,18 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,22 +7372,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7394,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7424,22 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,18 +7642,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,18 +7686,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,17 +7860,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -7886,19 +7886,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7912,15 +7908,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,18 +7934,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7960,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,22 +7982,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,18 +8096,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,22 +8122,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,22 +8148,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8182,26 +8178,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8212,18 +8208,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8238,26 +8234,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8268,22 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8294,18 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8320,26 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -8542,22 +8542,18 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,26 +8568,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8602,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8632,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8662,20 +8658,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
         <v>2</v>
       </c>
@@ -8688,26 +8676,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -8718,12 +8706,24 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F333" t="n">
         <v>2</v>
       </c>
@@ -8736,22 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,22 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -8930,22 +8930,18 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8956,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8990,26 +8982,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9020,22 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9046,22 +9042,26 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9616,18 +9616,22 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9642,14 +9646,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -9660,22 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9686,22 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,17 +9928,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -9954,15 +9954,19 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>3</v>
@@ -9976,12 +9980,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,12 +10002,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10020,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10068,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10090,22 +10094,18 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,14 +10414,14 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="406">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,14 +10450,14 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,14 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,22 +10928,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10950,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -10972,22 +10976,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -10998,22 +11002,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11028,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11072,18 +11076,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,22 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -11504,18 +11500,14 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11556,14 +11548,18 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11578,18 +11574,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12228,18 +12228,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12250,14 +12246,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -12474,22 +12474,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12570,18 +12566,22 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -13086,16 +13086,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
         <v>3</v>
       </c>
@@ -13108,18 +13104,22 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13148,22 +13148,18 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -13174,12 +13170,16 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13210,18 +13210,18 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F541" t="n">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -14380,22 +14380,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14406,22 +14402,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14432,18 +14428,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -14458,22 +14454,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
@@ -14484,18 +14480,22 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F604" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="605">
@@ -14506,18 +14506,18 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F605" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15898,14 +15898,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -15934,14 +15934,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15970,14 +15970,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16060,14 +16060,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="691">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,18 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1738,19 +1742,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1768,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,26 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1858,18 +1858,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,22 +2376,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2402,19 +2398,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2428,22 +2420,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2454,15 +2442,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2476,18 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,18 +2516,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2942,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2968,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3088,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,10 +3330,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3588,18 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,26 +3618,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3644,26 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,22 +3674,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,18 +3700,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3745,11 +3745,11 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,18 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4062,26 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4092,22 +4092,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,22 +4122,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,26 +4152,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,20 +4612,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4630,26 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4660,22 +4664,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4690,22 +4694,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4716,26 +4724,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4746,20 +4754,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4772,16 +4776,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4794,12 +4806,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4816,24 +4828,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4846,16 +4850,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,26 +4876,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4898,26 +4906,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4928,22 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4958,26 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4988,16 +4992,20 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5010,26 +5018,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5378,18 +5378,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5404,22 +5404,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,26 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5460,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5494,22 +5490,26 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,22 +6176,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6202,22 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6228,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6250,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6272,18 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,22 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6560,26 +6560,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6586,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6616,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6650,22 +6646,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,22 +7342,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7372,26 +7368,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -7402,22 +7394,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7424,22 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,18 +7642,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -7664,18 +7664,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -7816,18 +7816,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -7838,12 +7842,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,22 +7864,18 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,19 +7908,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,17 +7930,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
@@ -7960,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7982,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8004,15 +8000,19 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>3</v>
@@ -8096,18 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,22 +8126,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8148,26 +8156,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8178,26 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -8208,18 +8212,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8234,26 +8238,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,22 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8324,18 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -8568,22 +8568,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,22 +8598,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8658,12 +8658,24 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F331" t="n">
         <v>2</v>
       </c>
@@ -8676,26 +8688,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8706,26 +8718,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8736,26 +8748,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8766,22 +8778,18 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8796,20 +8804,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -8930,22 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8956,22 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8982,26 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9012,22 +9016,18 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9042,26 +9042,26 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9616,22 +9616,18 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9646,22 +9642,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -9672,14 +9660,22 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9686,22 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,22 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9980,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10002,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10024,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10046,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,17 +10064,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -10094,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,15 +10112,19 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>3</v>
@@ -10378,14 +10378,14 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,14 +10450,14 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,18 +10902,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,18 +10924,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -10950,22 +10950,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10976,22 +10972,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -11002,22 +10998,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -11028,18 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -11050,22 +11050,18 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11076,14 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,18 +11478,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11500,14 +11504,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11548,18 +11556,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11574,22 +11578,18 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11846,7 +11846,7 @@
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -12210,14 +12210,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12228,7 +12232,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12246,18 +12250,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12454,7 +12454,7 @@
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -12474,18 +12474,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -12566,22 +12570,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -12620,7 +12620,7 @@
       <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -12940,7 +12940,11 @@
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E528" t="inlineStr">
         <is>
           <t>1879.0K</t>
@@ -13000,7 +13004,7 @@
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -13026,7 +13030,7 @@
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -13086,12 +13090,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F535" t="n">
         <v>3</v>
       </c>
@@ -13104,18 +13112,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F536" t="n">
@@ -13130,7 +13138,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13148,16 +13156,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13170,18 +13174,22 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F539" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -13192,7 +13200,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13210,22 +13218,18 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -13236,7 +13240,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13258,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13314,7 +13318,7 @@
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -13432,7 +13436,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13454,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -14160,7 +14164,7 @@
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -14184,7 +14188,11 @@
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>51.3</t>
@@ -14282,7 +14290,7 @@
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -14380,18 +14388,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14402,18 +14414,18 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -14428,22 +14440,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D602" t="inlineStr"/>
       <c r="E602" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -14454,22 +14462,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -14480,18 +14488,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -14506,22 +14514,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -14630,7 +14638,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14648,7 +14656,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -15484,7 +15492,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15510,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15646,7 +15654,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15672,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15844,7 +15852,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15898,14 +15906,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -15934,14 +15942,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -15952,14 +15960,14 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr"/>
       <c r="F684" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
@@ -15970,14 +15978,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -15988,7 +15996,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16006,7 +16014,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16060,7 +16068,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16240,7 +16248,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16276,7 +16284,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16294,7 +16302,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16312,7 +16320,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F717"/>
+  <dimension ref="A1:F730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,26 +1712,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1742,18 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1768,19 +1772,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1798,26 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,18 +1828,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,22 +2332,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2380,22 +2376,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2406,19 +2398,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2432,18 +2420,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2454,15 +2446,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2476,18 +2472,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2968,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3088,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,10 +3330,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,18 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3584,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3614,18 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3640,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3670,12 +3678,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3685,11 +3693,11 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3700,26 +3708,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3730,22 +3734,18 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,26 +4036,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4066,22 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,26 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4152,22 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,22 +4612,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4630,26 +4642,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4660,26 +4672,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4690,7 +4702,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4700,16 +4712,16 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4720,18 +4732,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4746,12 +4762,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4768,16 +4784,20 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4790,20 +4810,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4816,12 +4832,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4838,24 +4854,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,26 +4876,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4898,22 +4902,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4928,26 +4932,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4958,26 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -4988,18 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5010,26 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,22 +5408,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,18 +5434,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,26 +5460,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -5494,18 +5490,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>77.6%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5968,26 +5968,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -6028,22 +6024,26 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -6080,18 +6080,18 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexJAN</t>
+          <t>Kansas Fed Composite IndexJAN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -6106,18 +6106,18 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexJAN</t>
+          <t>Kansas Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,17 +6242,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>2.5M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,15 +6290,19 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6312,17 +6316,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2.5M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -6338,12 +6342,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,19 +6364,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6560,22 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6586,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6616,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -7204,18 +7204,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7230,18 +7234,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7256,26 +7260,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
           <t>4.3%</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7286,22 +7286,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7316,22 +7312,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,18 +7664,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -7816,19 +7816,15 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
         <v>3</v>
@@ -7842,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7864,18 +7860,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,22 +7908,18 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -7934,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,22 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8004,18 +8000,22 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -8096,26 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -8126,18 +8126,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,22 +8156,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8182,18 +8186,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8208,18 +8212,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8234,22 +8238,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -8260,26 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8290,22 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8320,7 +8324,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -8328,18 +8332,14 @@
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/30</t>
+          <t>15-Year Mortgage RateJAN/30</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>6.12%</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/30</t>
+          <t>30-Year Mortgage RateJAN/30</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,14 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8590,22 +8602,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8616,19 +8632,15 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8646,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8676,15 +8688,19 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8702,26 +8718,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8732,26 +8744,14 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8762,26 +8762,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8792,26 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -9616,18 +9616,22 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9642,14 +9646,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -9660,18 +9672,18 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -9686,26 +9698,14 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
       <c r="F373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="374">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,19 +9954,15 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
         <v>3</v>
@@ -9976,22 +9976,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -10002,18 +9998,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10046,15 +10046,19 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10068,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,12 +10116,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10378,14 +10378,14 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,14 +10432,14 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,22 +10880,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="429">
@@ -10906,18 +10906,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10932,14 +10928,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10954,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432">
@@ -10976,22 +10976,18 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -11002,22 +10998,18 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11028,14 +11020,14 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11050,14 +11042,18 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11072,18 +11068,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -11094,22 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/13</t>
+          <t>30-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/13</t>
+          <t>15-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -11478,22 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -11504,18 +11500,14 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11530,18 +11522,18 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -11556,18 +11548,22 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -11578,14 +11574,18 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F459" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
@@ -12174,14 +12174,18 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -12246,18 +12250,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -12322,14 +12322,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -12430,14 +12430,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr"/>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -12448,18 +12448,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12474,18 +12474,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -12496,14 +12500,14 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F506" t="n">
@@ -12518,22 +12522,18 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="508">
@@ -12544,18 +12544,22 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F508" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -12566,22 +12570,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -12592,22 +12592,18 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="511">
@@ -12618,18 +12614,22 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -12900,22 +12900,14 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr"/>
       <c r="F526" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="527">
@@ -12952,22 +12944,22 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F528" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="529">
@@ -12978,14 +12970,14 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F529" t="n">
@@ -13000,14 +12992,22 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
-      <c r="D530" t="inlineStr"/>
-      <c r="E530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13036,7 +13036,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13054,14 +13054,22 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr"/>
-      <c r="E533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F533" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -13072,7 +13080,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13090,12 +13098,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F535" t="n">
         <v>3</v>
       </c>
@@ -13108,16 +13120,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13130,22 +13138,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13192,22 +13192,18 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
+      <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F540" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -13222,7 +13218,11 @@
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>1879.0K</t>
@@ -13240,7 +13240,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13318,7 +13318,7 @@
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13580,14 +13580,14 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr"/>
       <c r="F560" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="561">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
@@ -13634,14 +13634,14 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
       <c r="F563" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="564">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13670,14 +13670,14 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr"/>
       <c r="F565" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="566">
@@ -13688,14 +13688,14 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="567">
@@ -13706,14 +13706,14 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
@@ -13760,14 +13760,14 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr"/>
       <c r="F570" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
@@ -13814,14 +13814,14 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr"/>
       <c r="F573" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="574">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -13850,14 +13850,14 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr"/>
       <c r="F575" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -14066,14 +14066,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14088,15 +14092,11 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14114,18 +14114,18 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14162,18 +14162,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14188,18 +14188,18 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -14214,22 +14214,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F593" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="594">
@@ -14240,18 +14240,18 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -14266,22 +14266,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F595" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -14292,22 +14292,18 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -14318,22 +14314,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598">
@@ -14344,18 +14340,18 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F598" t="n">
@@ -14370,18 +14366,18 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -14396,18 +14392,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14418,18 +14418,18 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -14444,22 +14444,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -14470,18 +14470,14 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F603" t="n">
@@ -14496,18 +14492,22 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>4.13M</t>
+        </is>
+      </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F604" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605">
@@ -14518,22 +14518,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -14544,18 +14544,18 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F606" t="n">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -14912,14 +14912,18 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr"/>
-      <c r="E626" t="inlineStr"/>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F626" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="627">
@@ -14930,14 +14934,18 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr"/>
-      <c r="E627" t="inlineStr"/>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -14948,7 +14956,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -14966,18 +14974,14 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr"/>
-      <c r="E629" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E629" t="inlineStr"/>
       <c r="F629" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="630">
@@ -14988,7 +14992,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -15006,18 +15010,14 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr"/>
-      <c r="E631" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E631" t="inlineStr"/>
       <c r="F631" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="632">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15082,14 +15082,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15118,7 +15118,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -15136,14 +15136,14 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr"/>
       <c r="F638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -15406,7 +15406,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15460,14 +15460,14 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr"/>
       <c r="F656" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="657">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -15496,14 +15496,14 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr"/>
       <c r="E658" t="inlineStr"/>
       <c r="F658" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="659">
@@ -15514,14 +15514,14 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr"/>
       <c r="F659" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="660">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15586,14 +15586,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15730,7 +15730,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -15748,14 +15748,14 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr"/>
       <c r="F672" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="673">
@@ -15766,14 +15766,14 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr"/>
       <c r="F673" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="674">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15874,14 +15874,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -15892,14 +15892,14 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr"/>
       <c r="F680" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -15982,14 +15982,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -16000,14 +16000,14 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="687">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16036,14 +16036,14 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr"/>
       <c r="E688" t="inlineStr"/>
       <c r="F688" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="689">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16072,14 +16072,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="691">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16216,7 +16216,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16324,7 +16324,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16400,12 +16400,20 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
-      <c r="D708" t="inlineStr"/>
-      <c r="E708" t="inlineStr"/>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F708" t="n">
         <v>3</v>
       </c>
@@ -16418,20 +16426,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
-      <c r="D709" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E709" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" t="inlineStr"/>
       <c r="F709" t="n">
         <v>3</v>
       </c>
@@ -16444,14 +16444,14 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="711">
@@ -16550,20 +16550,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
-      <c r="D715" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E715" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D715" t="inlineStr"/>
+      <c r="E715" t="inlineStr"/>
       <c r="F715" t="n">
         <v>3</v>
       </c>
@@ -16576,14 +16568,22 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F716" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="717">
@@ -16594,17 +16594,291 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr">
+      <c r="E717" t="inlineStr"/>
+      <c r="F717" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr"/>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="F718" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Durable Goods Orders MoMJAN</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr"/>
+      <c r="D719" t="inlineStr"/>
+      <c r="E719" t="inlineStr"/>
+      <c r="F719" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr"/>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="F720" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr"/>
+      <c r="D721" t="inlineStr"/>
+      <c r="E721" t="inlineStr"/>
+      <c r="F721" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr"/>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="F722" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Continuing Jobless ClaimsFEB/15</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr"/>
+      <c r="D723" t="inlineStr"/>
+      <c r="E723" t="inlineStr"/>
+      <c r="F723" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F724" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr"/>
+      <c r="D725" t="inlineStr"/>
+      <c r="E725" t="inlineStr"/>
+      <c r="F725" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr"/>
+      <c r="D726" t="inlineStr"/>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F726" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr"/>
+      <c r="D727" t="inlineStr"/>
+      <c r="E727" t="inlineStr"/>
+      <c r="F727" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr"/>
+      <c r="D728" t="inlineStr"/>
+      <c r="E728" t="inlineStr"/>
+      <c r="F728" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr"/>
+      <c r="D729" t="inlineStr"/>
+      <c r="E729" t="inlineStr">
         <is>
           <t>4.2%</t>
         </is>
       </c>
-      <c r="F717" t="n">
+      <c r="F729" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2025-02-27 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr"/>
+      <c r="D730" t="inlineStr"/>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="F730" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F730"/>
+  <dimension ref="A1:F734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,19 +1798,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1828,18 +1824,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,26 +1854,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1884,26 +1884,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,18 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,15 +2402,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2420,22 +2428,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,19 +2450,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,18 +2516,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,26 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3648,26 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3678,26 +3670,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3708,18 +3700,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3734,18 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4096,22 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,18 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,26 +4156,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,26 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -4642,26 +4638,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4672,22 +4660,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4702,26 +4690,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4732,24 +4716,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4762,12 +4738,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4784,20 +4760,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4810,18 +4782,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4832,12 +4812,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4854,18 +4834,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4876,22 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,16 +4924,20 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4954,7 +4950,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4964,16 +4960,16 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4980,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5014,18 +5010,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5408,18 +5408,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,18 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>77.6%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5460,26 +5464,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -5490,22 +5494,18 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5968,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -6024,26 +6028,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -6080,18 +6080,18 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexJAN</t>
+          <t>Kansas Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -6106,18 +6106,18 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexJAN</t>
+          <t>Kansas Fed Composite IndexJAN</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,17 +6242,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2.5M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -6268,15 +6268,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6290,19 +6294,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6316,17 +6316,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>2.5M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -6342,12 +6342,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6364,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6560,26 +6560,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6586,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6616,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7204,22 +7204,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7234,22 +7230,26 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -7260,18 +7260,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7286,18 +7286,22 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7312,26 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
           <t>4.3%</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7816,18 +7816,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -7838,15 +7842,19 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>3</v>
@@ -7860,22 +7868,18 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -7886,12 +7890,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,12 +7934,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7952,18 +7956,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7974,19 +7982,15 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
         <v>3</v>
@@ -8000,22 +8004,18 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8104,18 +8104,14 @@
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8126,22 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,26 +8152,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8186,22 +8178,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8212,22 +8208,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8238,26 +8238,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8268,18 +8264,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,26 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -8324,18 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8350,22 +8350,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8380,18 +8376,22 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8572,22 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8602,26 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8632,15 +8628,19 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8658,24 +8658,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
         <v>2</v>
       </c>
@@ -8688,19 +8676,15 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8718,22 +8702,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -8744,14 +8732,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8762,26 +8762,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8792,26 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.155%</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>4.155%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,18 +9660,22 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -9698,14 +9690,22 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr"/>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F373" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9820,18 +9824,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9846,18 +9850,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9872,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9898,26 +9902,22 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F381" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,15 +9972,19 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>3</v>
@@ -9998,22 +9998,18 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -10024,18 +10020,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10046,19 +10046,15 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10072,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10094,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,18 +10112,22 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,14 +10396,14 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,14 +10432,14 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="407">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10468,18 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10494,22 +10494,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10520,22 +10520,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,18 +10572,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,22 +10880,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -10906,18 +10906,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -10928,14 +10932,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10950,22 +10958,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10976,14 +10980,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,14 +11002,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11020,18 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -11042,18 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11068,22 +11072,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -11094,22 +11098,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,14 +11290,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
@@ -11308,22 +11312,18 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11334,22 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11360,18 +11356,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -11382,22 +11382,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -11408,22 +11408,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11434,18 +11430,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
@@ -12080,14 +12080,14 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="485">
@@ -12134,14 +12134,14 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -12152,18 +12152,14 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="489">
@@ -12196,7 +12192,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12214,7 +12210,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12232,14 +12228,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -12322,14 +12322,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -12394,14 +12394,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12448,18 +12448,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>1.4M</t>
+          <t>1.46M</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12474,18 +12474,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12570,18 +12570,22 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -12614,22 +12618,18 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
@@ -12944,22 +12944,22 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529">
@@ -12970,16 +12970,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
         <v>3</v>
       </c>
@@ -12992,22 +12988,14 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E530" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D530" t="inlineStr"/>
+      <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -13018,14 +13006,22 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
-      <c r="E531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -13036,7 +13032,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13054,22 +13050,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13080,12 +13068,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F534" t="n">
         <v>3</v>
       </c>
@@ -13098,18 +13090,22 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -13120,14 +13116,22 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13138,7 +13142,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13156,7 +13160,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13174,7 +13178,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13192,16 +13196,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E540" t="inlineStr"/>
       <c r="F540" t="n">
         <v>3</v>
       </c>
@@ -13214,18 +13214,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+      <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F541" t="n">
@@ -13240,12 +13236,20 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
-      <c r="D542" t="inlineStr"/>
-      <c r="E542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F542" t="n">
         <v>3</v>
       </c>
@@ -13258,7 +13262,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13400,7 +13404,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -13418,7 +13422,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
@@ -13436,7 +13440,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13454,7 +13458,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -13472,7 +13476,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
@@ -13508,7 +13512,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13526,7 +13530,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -13544,14 +13548,14 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -13562,7 +13566,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13580,7 +13584,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -13598,14 +13602,14 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
       <c r="F561" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="562">
@@ -13616,14 +13620,14 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr"/>
       <c r="F562" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="563">
@@ -13634,7 +13638,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13652,7 +13656,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13670,14 +13674,14 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr"/>
       <c r="F565" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="566">
@@ -13688,14 +13692,14 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="567">
@@ -13706,14 +13710,14 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="568">
@@ -13724,14 +13728,14 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="569">
@@ -13742,7 +13746,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
@@ -13760,7 +13764,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
@@ -13778,7 +13782,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
@@ -13796,7 +13800,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
@@ -13814,7 +13818,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -13832,7 +13836,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -13850,7 +13854,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -13868,14 +13872,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr"/>
       <c r="F576" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -14066,18 +14070,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14092,14 +14096,18 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -14114,15 +14122,11 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14140,11 +14144,15 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14188,15 +14196,11 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14214,18 +14218,18 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F593" t="n">
@@ -14240,22 +14244,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F594" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="595">
@@ -14266,22 +14270,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F595" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="596">
@@ -14292,18 +14296,22 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
@@ -14314,22 +14322,18 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>4.13M</t>
-        </is>
-      </c>
+      <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598">
@@ -14340,18 +14344,18 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F598" t="n">
@@ -14366,18 +14370,18 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -14392,18 +14396,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F600" t="n">
@@ -14444,22 +14448,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -14470,14 +14474,18 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
-      <c r="D603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F603" t="n">
@@ -14492,22 +14500,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>4.13M</t>
-        </is>
-      </c>
+      <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F604" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -14518,22 +14522,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="606">
@@ -14624,7 +14628,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14642,7 +14646,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14768,7 +14772,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14804,7 +14808,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
@@ -14894,7 +14898,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -14912,18 +14916,14 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr"/>
-      <c r="E626" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E626" t="inlineStr"/>
       <c r="F626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="627">
@@ -14934,18 +14934,14 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr"/>
-      <c r="E627" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E627" t="inlineStr"/>
       <c r="F627" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="628">
@@ -14974,7 +14970,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -15010,14 +15006,18 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr"/>
-      <c r="E631" t="inlineStr"/>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F631" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="632">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15046,14 +15046,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr"/>
-      <c r="E633" t="inlineStr"/>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F633" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="634">
@@ -15100,7 +15104,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15118,7 +15122,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -15136,14 +15140,14 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr"/>
       <c r="F638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -15154,7 +15158,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15172,14 +15176,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15190,14 +15194,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
       <c r="F641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -15208,14 +15212,14 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr"/>
       <c r="F642" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="643">
@@ -15244,7 +15248,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -15262,7 +15266,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
@@ -15406,7 +15410,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15424,14 +15428,14 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr"/>
       <c r="E654" t="inlineStr"/>
       <c r="F654" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="655">
@@ -15442,7 +15446,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15460,14 +15464,14 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr"/>
       <c r="F656" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="657">
@@ -15496,7 +15500,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15514,7 +15518,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15532,14 +15536,14 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr"/>
       <c r="F660" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="661">
@@ -15550,7 +15554,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15568,7 +15572,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15586,14 +15590,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="664">
@@ -15604,7 +15608,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -15622,7 +15626,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -15640,7 +15644,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15658,7 +15662,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15712,7 +15716,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15730,7 +15734,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -15748,7 +15752,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -15766,14 +15770,14 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr"/>
       <c r="F673" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="674">
@@ -15784,7 +15788,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -15802,7 +15806,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -15820,7 +15824,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -15838,7 +15842,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -15856,7 +15860,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15874,14 +15878,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680">
@@ -15892,7 +15896,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -15910,14 +15914,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -15928,7 +15932,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -15946,7 +15950,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -15964,7 +15968,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15982,7 +15986,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16000,14 +16004,14 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
@@ -16018,7 +16022,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16036,14 +16040,14 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr"/>
       <c r="E688" t="inlineStr"/>
       <c r="F688" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="689">
@@ -16054,7 +16058,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16072,14 +16076,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="691">
@@ -16162,7 +16166,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16180,7 +16184,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16198,7 +16202,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16216,7 +16220,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16234,7 +16238,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16270,7 +16274,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16288,7 +16292,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16342,14 +16346,22 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
-      <c r="D705" t="inlineStr"/>
-      <c r="E705" t="inlineStr"/>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="706">
@@ -16360,14 +16372,14 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
       <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr"/>
       <c r="F706" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="707">
@@ -16378,16 +16390,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr"/>
-      <c r="E707" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="E707" t="inlineStr"/>
       <c r="F707" t="n">
         <v>3</v>
       </c>
@@ -16400,22 +16408,22 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
       <c r="D708" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F708" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="709">
@@ -16426,14 +16434,14 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
       <c r="D709" t="inlineStr"/>
       <c r="E709" t="inlineStr"/>
       <c r="F709" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="710">
@@ -16444,14 +16452,14 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="711">
@@ -16462,22 +16470,22 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
       <c r="D711" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F711" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="712">
@@ -16488,14 +16496,14 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
       <c r="D712" t="inlineStr"/>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="713">
@@ -16506,22 +16514,14 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
-      <c r="D713" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E713" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D713" t="inlineStr"/>
+      <c r="E713" t="inlineStr"/>
       <c r="F713" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="714">
@@ -16532,14 +16532,18 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr"/>
-      <c r="E714" t="inlineStr"/>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F714" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="715">
@@ -16550,12 +16554,20 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
-      <c r="D715" t="inlineStr"/>
-      <c r="E715" t="inlineStr"/>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F715" t="n">
         <v>3</v>
       </c>
@@ -16568,22 +16580,14 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E716" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D716" t="inlineStr"/>
+      <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717">
@@ -16594,14 +16598,14 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
       <c r="F717" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="718">
@@ -16612,18 +16616,14 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F718" t="n">
@@ -16638,14 +16638,14 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="720">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
         </is>
       </c>
       <c r="F720" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="721">
@@ -16682,14 +16682,14 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="722">
@@ -16700,22 +16700,22 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F722" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="723">
@@ -16726,14 +16726,14 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr"/>
       <c r="F723" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="724">
@@ -16744,22 +16744,22 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F724" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="725">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
@@ -16788,14 +16788,18 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
-      <c r="D726" t="inlineStr"/>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F726" t="n">
@@ -16810,7 +16814,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -16828,12 +16832,16 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr"/>
-      <c r="E728" t="inlineStr"/>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F728" t="n">
         <v>3</v>
       </c>
@@ -16846,16 +16854,12 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr"/>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E729" t="inlineStr"/>
       <c r="F729" t="n">
         <v>3</v>
       </c>
@@ -16879,6 +16883,82 @@
         </is>
       </c>
       <c r="F730" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2025-02-27 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Pending Home Sales YoYJAN</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr"/>
+      <c r="D731" t="inlineStr"/>
+      <c r="E731" t="inlineStr"/>
+      <c r="F731" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2025-02-27 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Pending Home Sales MoMJAN</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr"/>
+      <c r="D732" t="inlineStr"/>
+      <c r="E732" t="inlineStr"/>
+      <c r="F732" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2025-02-27 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr"/>
+      <c r="D733" t="inlineStr"/>
+      <c r="E733" t="inlineStr"/>
+      <c r="F733" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2025-02-27 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr"/>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr"/>
+      <c r="F734" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F742"/>
+  <dimension ref="A1:F748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,22 +790,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -816,15 +812,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,22 +838,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -864,19 +860,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -890,18 +882,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -912,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,18 +930,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,15 +1772,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1798,22 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1888,18 +1888,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2124,26 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2154,18 +2154,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2180,14 +2184,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2198,22 +2210,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2228,24 +2240,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
         <v>2</v>
       </c>
@@ -2332,15 +2332,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>3</v>
@@ -2354,22 +2358,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2402,18 +2402,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2446,19 +2450,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-2.502M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,18 +2494,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>5K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,22 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3054,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3084,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,14 +3308,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3330,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3352,12 +3348,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3374,10 +3370,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
@@ -3558,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,26 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3648,22 +3644,18 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3678,18 +3670,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3700,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3734,7 +3730,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3742,10 +3738,14 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,22 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4322,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,18 +4348,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4370,22 +4374,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4396,18 +4396,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,19 +4422,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,26 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,22 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4660,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,22 +4690,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4728,26 +4720,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4758,12 +4742,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4780,26 +4764,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4810,18 +4790,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4836,12 +4820,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4858,18 +4842,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4880,26 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4910,18 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4962,22 +4958,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4988,24 +4988,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5018,18 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5040,26 +5040,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5070,17 +5070,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5378,18 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>77.6%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5404,22 +5408,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,26 +5434,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5464,18 +5464,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5490,26 +5490,26 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5968,26 +5968,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -6028,22 +6024,26 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,15 +6246,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6264,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,22 +6294,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,19 +6338,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,18 +6360,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6382,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,22 +6408,18 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -6560,26 +6560,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6586,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6620,22 +6616,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6646,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,22 +6676,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6710,26 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6740,22 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>4.24M</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7342,18 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,18 +7372,18 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7394,26 +7398,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7424,26 +7424,26 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8572,26 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8602,18 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,26 +8632,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8658,12 +8662,20 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F331" t="n">
         <v>2</v>
       </c>
@@ -8676,15 +8688,19 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8702,26 +8718,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8732,22 +8744,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8762,26 +8774,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8792,24 +8804,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -8930,26 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8956,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8990,22 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9042,26 +9046,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9824,18 +9820,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9876,18 +9872,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,22 +9898,26 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F381" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,15 +9972,19 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
         <v>3</v>
@@ -9994,17 +9998,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -10020,22 +10024,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10046,19 +10046,15 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10072,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10094,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,18 +10112,22 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -10468,22 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10494,18 +10490,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,22 +10516,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,18 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10598,14 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,18 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,22 +10928,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -10954,14 +10954,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10976,14 +10980,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,18 +11002,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -11020,18 +11028,14 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,22 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11072,22 +11076,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,22 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -11290,18 +11286,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11312,18 +11312,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11334,22 +11338,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11360,18 +11360,18 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -11382,14 +11382,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -11404,14 +11404,14 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11426,13 +11426,13 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -11452,22 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
@@ -12098,14 +12098,14 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="486">
@@ -12116,14 +12116,14 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
@@ -12192,14 +12192,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -12210,7 +12214,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12228,7 +12232,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12246,18 +12250,14 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -12286,14 +12286,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12304,14 +12304,14 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -12376,14 +12376,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr"/>
       <c r="F500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -12394,14 +12394,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12474,14 +12474,14 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12496,14 +12496,14 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F506" t="n">
@@ -12570,22 +12570,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -12596,14 +12592,14 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F510" t="n">
@@ -12618,18 +12614,22 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13020,14 +13020,22 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13038,7 +13046,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13056,20 +13064,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
-      <c r="E534" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D534" t="inlineStr"/>
+      <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
         <v>3</v>
       </c>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13100,22 +13100,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13126,22 +13118,22 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13152,7 +13144,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13170,14 +13162,22 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F539" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -13188,14 +13188,22 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -13228,18 +13236,18 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F542" t="n">
@@ -13254,22 +13262,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13530,14 +13530,14 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr"/>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -13602,14 +13602,14 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
       <c r="F561" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="562">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
@@ -13638,14 +13638,14 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
       <c r="F563" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564">
@@ -13656,14 +13656,14 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr"/>
       <c r="F564" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="565">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
@@ -13782,14 +13782,14 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="572">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
@@ -13818,14 +13818,14 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr"/>
       <c r="F573" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="574">
@@ -13836,14 +13836,14 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr"/>
       <c r="E574" t="inlineStr"/>
       <c r="F574" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -13854,14 +13854,14 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr"/>
       <c r="F575" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14096,15 +14096,11 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14122,11 +14118,15 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14144,18 +14144,14 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -14196,14 +14192,18 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -14218,22 +14218,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F593" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="594">
@@ -14244,22 +14244,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F594" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="595">
@@ -14270,22 +14270,18 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>4.13M</t>
-        </is>
-      </c>
+      <c r="D595" t="inlineStr"/>
       <c r="E595" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F595" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -14296,18 +14292,18 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F596" t="n">
@@ -14322,22 +14318,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14348,22 +14344,22 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -14374,22 +14370,18 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
-      <c r="D599" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -14400,22 +14392,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14426,18 +14418,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
-      <c r="D601" t="inlineStr"/>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>4.13M</t>
+        </is>
+      </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="602">
@@ -14448,18 +14444,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -14500,18 +14496,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -14526,22 +14522,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -14552,18 +14548,22 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
-      <c r="D606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F606" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14808,7 +14808,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -14992,14 +14992,18 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
       <c r="D630" t="inlineStr"/>
-      <c r="E630" t="inlineStr"/>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F630" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="631">
@@ -15010,7 +15014,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -15028,18 +15032,14 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
       <c r="D632" t="inlineStr"/>
-      <c r="E632" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E632" t="inlineStr"/>
       <c r="F632" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="633">
@@ -15050,7 +15050,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15086,14 +15086,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15122,14 +15122,14 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr"/>
       <c r="F637" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="638">
@@ -15140,14 +15140,14 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr"/>
       <c r="F638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -15176,14 +15176,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15464,14 +15464,14 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr"/>
       <c r="E656" t="inlineStr"/>
       <c r="F656" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="657">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15518,14 +15518,14 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr"/>
       <c r="F659" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="660">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15572,14 +15572,14 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr"/>
       <c r="F662" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="663">
@@ -15590,14 +15590,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -15626,7 +15626,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -15788,14 +15788,14 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr"/>
       <c r="F674" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -15824,14 +15824,14 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr"/>
       <c r="F676" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="677">
@@ -15842,14 +15842,14 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr"/>
       <c r="F677" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15878,14 +15878,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680">
@@ -15896,7 +15896,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -15914,14 +15914,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -15950,14 +15950,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16076,7 +16076,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
@@ -16346,12 +16346,20 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
-      <c r="D705" t="inlineStr"/>
-      <c r="E705" t="inlineStr"/>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F705" t="n">
         <v>1</v>
       </c>
@@ -16364,20 +16372,12 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
-      <c r="D706" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E706" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D706" t="inlineStr"/>
+      <c r="E706" t="inlineStr"/>
       <c r="F706" t="n">
         <v>1</v>
       </c>
@@ -16390,14 +16390,14 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr"/>
       <c r="E707" t="inlineStr"/>
       <c r="F707" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="708">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16514,14 +16514,18 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
-      <c r="D713" t="inlineStr"/>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F713" t="n">
@@ -16536,14 +16540,14 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715">
@@ -16554,12 +16558,16 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr"/>
-      <c r="E715" t="inlineStr"/>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F715" t="n">
         <v>3</v>
       </c>
@@ -16572,22 +16580,22 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F716" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717">
@@ -16598,14 +16606,14 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F717" t="n">
@@ -16620,20 +16628,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="inlineStr"/>
       <c r="F718" t="n">
         <v>3</v>
       </c>
@@ -16646,16 +16646,12 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr"/>
-      <c r="E719" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E719" t="inlineStr"/>
       <c r="F719" t="n">
         <v>3</v>
       </c>
@@ -16668,7 +16664,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -16686,14 +16682,22 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
-      <c r="D721" t="inlineStr"/>
-      <c r="E721" t="inlineStr"/>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F721" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="722">
@@ -16704,12 +16708,20 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr"/>
-      <c r="E722" t="inlineStr"/>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F722" t="n">
         <v>1</v>
       </c>
@@ -16722,14 +16734,14 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F723" t="n">
@@ -16744,14 +16756,14 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr"/>
       <c r="F724" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="725">
@@ -16788,14 +16800,14 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr"/>
       <c r="F726" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="727">
@@ -16806,20 +16818,12 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E727" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D727" t="inlineStr"/>
+      <c r="E727" t="inlineStr"/>
       <c r="F727" t="n">
         <v>3</v>
       </c>
@@ -16832,12 +16836,16 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr"/>
-      <c r="E728" t="inlineStr"/>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F728" t="n">
         <v>3</v>
       </c>
@@ -16850,22 +16858,14 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D729" t="inlineStr"/>
+      <c r="E729" t="inlineStr"/>
       <c r="F729" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="730">
@@ -16876,14 +16876,14 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr"/>
       <c r="F730" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="731">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -16912,7 +16912,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -16984,11 +16984,15 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
-      <c r="D736" t="inlineStr"/>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E736" t="inlineStr"/>
       <c r="F736" t="n">
         <v>3</v>
@@ -17002,15 +17006,11 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
-      <c r="D737" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D737" t="inlineStr"/>
       <c r="E737" t="inlineStr"/>
       <c r="F737" t="n">
         <v>3</v>
@@ -17046,7 +17046,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17064,7 +17064,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17077,12 +17077,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -17095,12 +17095,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2025-02-27 22:00:00+05:30</t>
+          <t>2025-02-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17110,6 +17110,114 @@
         <v>3</v>
       </c>
     </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2025-02-27 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>4-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr"/>
+      <c r="D743" t="inlineStr"/>
+      <c r="E743" t="inlineStr"/>
+      <c r="F743" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2025-02-27 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>8-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr"/>
+      <c r="D744" t="inlineStr"/>
+      <c r="E744" t="inlineStr"/>
+      <c r="F744" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2025-02-27 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>4-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr"/>
+      <c r="D745" t="inlineStr"/>
+      <c r="E745" t="inlineStr"/>
+      <c r="F745" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2025-02-27 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>8-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr"/>
+      <c r="D746" t="inlineStr"/>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2025-02-27 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>15-Year Mortgage RateFEB/27</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr"/>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" t="inlineStr"/>
+      <c r="F747" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2025-02-27 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>30-Year Mortgage RateFEB/27</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr"/>
+      <c r="D748" t="inlineStr"/>
+      <c r="E748" t="inlineStr"/>
+      <c r="F748" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -746,22 +746,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -772,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -794,22 +790,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -820,15 +812,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -842,18 +838,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -864,19 +864,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -890,18 +886,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -912,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,15 +1798,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1824,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,22 +1888,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2124,14 +2124,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2142,26 +2150,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2172,22 +2180,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2202,24 +2210,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
         <v>2</v>
       </c>
@@ -2232,18 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2332,18 +2332,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2354,15 +2358,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
         <v>3</v>
@@ -2376,22 +2384,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2402,12 +2406,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2446,22 +2450,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-2.502M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2472,18 +2472,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2516,19 +2520,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>3</v>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>5K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,22 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3054,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3084,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,26 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3648,22 +3644,18 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3678,7 +3670,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3686,10 +3678,14 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3700,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3734,18 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,22 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4322,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,18 +4370,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4392,18 +4396,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,19 +4422,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4440,12 +4444,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4462,22 +4466,18 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -4582,26 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,22 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4660,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,18 +4690,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4720,26 +4720,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,12 +4742,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4772,22 +4764,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -4802,24 +4794,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4832,12 +4816,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4854,18 +4838,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4876,26 +4868,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,18 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4928,26 +4928,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4958,22 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4984,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5014,18 +5010,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5070,26 +5070,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,18 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>77.6%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,18 +5438,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5460,26 +5464,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -5490,22 +5494,18 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5968,26 +5968,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -6028,22 +6024,26 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,22 +6224,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6246,15 +6246,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,18 +6294,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6312,12 +6320,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,19 +6342,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,22 +6408,18 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -6560,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6620,22 +6620,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,22 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>4.24M</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6676,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6706,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6740,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7342,26 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7372,26 +7368,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7402,18 +7398,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,18 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8568,12 +8572,20 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8586,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8616,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8646,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8676,22 +8688,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8706,26 +8718,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8736,24 +8748,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8766,26 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8796,15 +8792,19 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8930,26 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8986,26 +8986,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9824,18 +9820,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9850,18 +9846,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9876,22 +9872,26 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -9902,18 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,19 +9994,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10020,22 +10016,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10046,18 +10042,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -10468,22 +10468,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -10494,22 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -10520,18 +10516,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,14 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,14 +10620,14 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -11264,22 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11290,18 +11286,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11312,18 +11312,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11334,18 +11338,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11356,22 +11364,18 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -11382,22 +11386,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11408,22 +11408,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11434,18 +11430,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
@@ -12098,14 +12098,14 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="486">
@@ -12134,14 +12134,14 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -12448,18 +12448,22 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -12566,22 +12570,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -12592,22 +12592,18 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="511">
@@ -12618,18 +12614,22 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -13108,14 +13108,22 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13126,22 +13134,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13152,14 +13152,18 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F538" t="n">
@@ -13174,22 +13178,14 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="540">
@@ -13200,7 +13196,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13218,18 +13214,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+      <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F541" t="n">
@@ -13244,14 +13236,22 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
-      <c r="D542" t="inlineStr"/>
-      <c r="E542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13476,14 +13476,14 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr"/>
       <c r="F554" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
@@ -13638,14 +13638,14 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
       <c r="F563" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
@@ -13728,14 +13728,14 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="569">
@@ -13746,14 +13746,14 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr"/>
       <c r="F569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="570">
@@ -14218,18 +14218,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>4.13M</t>
+        </is>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F593" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="594">
@@ -14240,18 +14244,14 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -14266,22 +14266,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F595" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15248,7 +15248,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -15734,14 +15734,14 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr"/>
       <c r="E671" t="inlineStr"/>
       <c r="F671" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="672">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -15788,14 +15788,14 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr"/>
       <c r="F674" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
@@ -15806,14 +15806,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -15824,14 +15824,14 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr"/>
       <c r="F676" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="677">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16076,7 +16076,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16572,14 +16572,14 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="717">
@@ -16608,22 +16608,14 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="inlineStr"/>
       <c r="F718" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="719">
@@ -16634,14 +16626,22 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr"/>
-      <c r="E719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F719" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="720">
@@ -16652,20 +16652,12 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E720" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D720" t="inlineStr"/>
+      <c r="E720" t="inlineStr"/>
       <c r="F720" t="n">
         <v>3</v>
       </c>
@@ -16678,22 +16670,22 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F721" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="722">
@@ -16704,7 +16696,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
@@ -16722,18 +16714,22 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr"/>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F723" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
@@ -16744,14 +16740,22 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
-      <c r="D724" t="inlineStr"/>
-      <c r="E724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F724" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="725">
@@ -16850,18 +16854,14 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F729" t="n">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17006,15 +17006,11 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
-      <c r="D737" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D737" t="inlineStr"/>
       <c r="E737" t="inlineStr"/>
       <c r="F737" t="n">
         <v>3</v>
@@ -17028,11 +17024,15 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
-      <c r="D738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E738" t="inlineStr"/>
       <c r="F738" t="n">
         <v>3</v>
@@ -17064,7 +17064,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-27.xlsx
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,22 +794,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -816,15 +816,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,12 +842,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,19 +864,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,18 +886,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/02</t>
+          <t>15-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/02</t>
+          <t>30-Year Mortgage RateJAN/02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,18 +1798,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1824,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1888,15 +1884,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -2124,22 +2124,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2154,14 +2154,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,24 +2180,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
         <v>2</v>
       </c>
@@ -2202,18 +2198,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2228,26 +2228,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,18 +2354,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2376,15 +2380,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2398,22 +2406,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2446,18 +2450,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2468,12 +2476,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2490,19 +2498,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2516,22 +2520,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-2.502M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>5K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,22 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3054,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3084,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,14 +3308,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3330,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3352,12 +3348,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3374,10 +3370,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
@@ -3558,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,26 +3614,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3648,22 +3644,18 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3678,18 +3670,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3700,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3734,7 +3730,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3742,10 +3738,14 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,22 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4322,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,22 +4348,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4374,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,19 +4418,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4444,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4466,18 +4462,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -4582,26 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,22 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4638,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4660,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,18 +4690,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4724,26 +4720,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4754,12 +4742,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4776,18 +4764,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4798,26 +4794,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4828,12 +4820,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4850,18 +4842,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4902,18 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4954,22 +4958,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4980,22 +4988,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5010,24 +5018,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,17 +5040,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -5070,22 +5070,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -5100,26 +5100,26 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -5378,18 +5378,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5404,26 +5404,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -5434,26 +5434,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5464,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5494,18 +5490,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>77.6%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5968,26 +5968,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -6028,22 +6024,26 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,18 +6224,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6242,15 +6250,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6264,12 +6276,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,12 +6298,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,12 +6320,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6330,19 +6342,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6356,22 +6364,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6382,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,22 +6408,18 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -6560,22 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>4.24M</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6586,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6616,22 +6620,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6646,26 +6650,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6676,22 +6676,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6706,26 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7342,18 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,18 +7372,18 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7394,26 +7398,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7424,26 +7424,26 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8572,26 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8602,18 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,12 +8632,20 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
+          <t>Employment Cost - Benefits QoQQ4</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
       <c r="F330" t="n">
         <v>2</v>
       </c>
@@ -8646,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8676,24 +8688,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="n">
         <v>2</v>
       </c>
@@ -8706,26 +8706,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8736,15 +8732,19 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8762,26 +8762,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -8930,26 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8956,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8982,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9020,22 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9046,22 +9042,26 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9616,26 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,18 +9634,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9794,18 +9794,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9820,22 +9820,26 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -9902,18 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,12 +9994,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10016,12 +10016,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10038,19 +10038,15 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10064,22 +10060,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,18 +10086,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -10468,18 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10494,22 +10494,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10520,22 +10520,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10546,14 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,18 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,14 +10620,14 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,18 +11290,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11308,18 +11316,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11330,18 +11342,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -11352,22 +11368,18 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -11378,22 +11390,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11404,22 +11412,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11430,18 +11434,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11452,22 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -12098,14 +12098,14 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="486">
@@ -12134,14 +12134,14 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -12448,18 +12448,22 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -12566,22 +12570,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -12592,22 +12592,18 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="511">
@@ -12618,18 +12614,22 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -13108,14 +13108,22 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13126,7 +13134,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13144,14 +13152,18 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F538" t="n">
@@ -13166,22 +13178,14 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="540">
@@ -13192,14 +13196,22 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -13210,18 +13222,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+      <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F541" t="n">
@@ -13236,7 +13244,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,22 +13262,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15086,14 +15086,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
@@ -15212,14 +15212,14 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr"/>
       <c r="F642" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="643">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16076,7 +16076,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16572,12 +16572,16 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr"/>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F716" t="n">
         <v>3</v>
       </c>
@@ -16608,14 +16612,14 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr"/>
       <c r="F718" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="719">
@@ -16626,14 +16630,14 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720">
@@ -16644,22 +16648,14 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E720" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D720" t="inlineStr"/>
+      <c r="E720" t="inlineStr"/>
       <c r="F720" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="721">
@@ -16670,14 +16666,22 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
-      <c r="D721" t="inlineStr"/>
-      <c r="E721" t="inlineStr"/>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F721" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="722">
@@ -16688,7 +16692,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
@@ -16706,20 +16710,12 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D723" t="inlineStr"/>
+      <c r="E723" t="inlineStr"/>
       <c r="F723" t="n">
         <v>3</v>
       </c>
@@ -16732,18 +16728,22 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
-      <c r="D724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F724" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="725">
@@ -16850,22 +16850,22 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F729" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="730">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17006,15 +17006,11 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
-      <c r="D737" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D737" t="inlineStr"/>
       <c r="E737" t="inlineStr"/>
       <c r="F737" t="n">
         <v>3</v>
@@ -17028,11 +17024,15 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
-      <c r="D738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E738" t="inlineStr"/>
       <c r="F738" t="n">
         <v>3</v>
